--- a/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
+++ b/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="249">
   <si>
     <t xml:space="preserve">Noen viktige lover: oppgaver til kapittel 20</t>
   </si>
@@ -77,7 +77,13 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder (Lovdata).</t>
   </si>
   <si>
+    <t xml:space="preserve">Lovlig</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Fjell Elektro: den første arbeidsavtalen Mona skriver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikke lovlig</t>
   </si>
   <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
@@ -180,7 +186,16 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Drøfte behovet for overtid med de tillitsvalgte før den settes i gang (§ 10-6 tredje ledd)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Nordlys: uka til Ronnys lag, og montøren med 212 overtidstimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be montørene jobbe inn timene uten tillegg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenting, så lenge montørene selv vil</t>
   </si>
   <si>
     <t xml:space="preserve">Ronny er formann på nybygg hos Nordlys. Laget hans hadde en travel uke: 7,5, 9, 11,5, 8, 10, 6 og 0 timer. Kari har også sett at en montør i laget har 212 overtidstimer de siste 52 ukene, og hun sier: «Så lenge de får betalt, er det vel greit?» Nordlys har avtalt 37,5 timers uke og har ingen avtale med tillitsvalgte om utvidet overtid.</t>
@@ -250,12 +265,27 @@
     <t xml:space="preserve">f) Kari sier: «Så lenge montørene får betalt, er det vel greit?» Forklar henne hvorfor det ikke holder. Bruk vilkåret for overtid og årsgrensen. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">20. mai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Nordlys: en oppsigelse som skal holde</t>
   </si>
   <si>
+    <t xml:space="preserve">31. mai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja</t>
+  </si>
+  <si>
     <t xml:space="preserve">En entreprenørkunde som sto for mye av arbeidet i prosjekt og nybygg, har gått konkurs. Kari må si opp én montør der. Hun har vurdert annet passende arbeid i service og i solceller og lading uten å finne noe. Valget faller på Jonas, 41 år, ansatt siden august 2020. Oppsigelsen gis 20. mars 2027. Ronny foreslår å «bare si det i bilen».</t>
   </si>
   <si>
+    <t xml:space="preserve">Nei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppsigelse skal drøftes med arbeidstakeren og den tillitsvalgte før beslutningen (§ 15-1), være skriftlig med rettigheter og frister (§ 15-4), ellers kan den kjennes ugyldig (§ 15-5), og være saklig begrunnet i virksomhetens, arbeidsgivers eller arbeidstakers forhold (§ 15-7). Fristene står i § 15-3 og løper fra første dag i måneden etter. Arbeidstakeren kan som hovedregel fortsette i stillingen mens saken går (§ 15-11).</t>
   </si>
   <si>
@@ -278,6 +308,15 @@
   </si>
   <si>
     <t xml:space="preserve">Frist fra 10 års ansettelse, måneder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja, oppsigelsestiden er ute 31. mai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei, han kan som hovedregel fortsette i stillingen til saken er avgjort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei, en oppsigelse han bestrider er automatisk ugyldig</t>
   </si>
   <si>
     <t xml:space="preserve">1. Regn hvor mange hele år Jonas har vært ansatt når oppsigelsen gis.
@@ -329,7 +368,16 @@
     <t xml:space="preserve">f) Hva gjør Kari, i hvilken rekkefølge, før og når hun skriver oppsigelsen? Tre setninger med paragraf.</t>
   </si>
   <si>
+    <t xml:space="preserve">§ 5 første ledd: utføre tjenesten fagmessig</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2A: Nordlys: fakturaen som sprakk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§ 7 andre ledd: kontakte forbrukeren når prisen blir betydelig høyere enn hun måtte vente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§ 32 første ledd: ta gjengs pris</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys skulle bytte sikringsskapet og trekke nye kurser i en enebolig. Kunden er en familie, altså en forbruker. Ida ga et skriftlig prisoverslag på 36 000 kr inkludert merverdiavgift. Underveis måtte flere kurser trekkes om, innenfor det som var avtalt. Montøren så at timene løp, men ringte ikke kunden. Fakturaen ble 42 300 kr, og kunden sier hun bare betaler 36 000.</t>
@@ -381,16 +429,49 @@
     <t xml:space="preserve">e) Kunden sier: «Jeg betaler 36 000, ikke en krone mer.» Hva svarer Kari, og hvilken rutine innfører hun så det ikke skjer igjen? Tre setninger med paragraf.</t>
   </si>
   <si>
+    <t xml:space="preserve">Montere vernet og legge det på fakturaen; det er praktisk å gjøre samtidig</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2B: Fjell Elektro: tre måter å si prisen på</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontakte kunden før han gjør tilleggsarbeidet (§ 9 første ledd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenting; fast pris betyr at alt nødvendig arbeid er inkludert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja, 15 % over overslaget er alltid lov</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mona selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift og har brukt tre ulike formuleringer om prisen i tilbudene. Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget, 2 500 kr. Mona spør hva hun kan fakturere, og hva tilbudsmalen bør si.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nei, 15 % er et tak; prisen skal ikke overstige overslaget vesentlig, og overskridelsen må kunne begrunnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei, et prisoverslag er det samme som fast pris</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fire prisformer, fra mest til minst bindende: fast pris, høyeste pris, prisoverslag (høyst 15 % over, § 32 andre ledd) og uforpliktende prisantydning. Er prisen ikke avtalt: gjengs pris (§ 32 første ledd). Tilleggsarbeid: kontakt forbrukeren først (§ 9); avtalt tilleggsarbeid kan kreves betalt (§ 33). Det er håndverkeren som må godtgjøre hvilken prisform som ble gitt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fast pris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Høyeste pris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisoverslag</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fjell Elektro selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift. Mona har brukt tre formuleringer i tilbudene: «fast pris 15 300 kr» (kunde 1), «prisoverslag 15 300 kr» (kunde 2) og «ca. 15 000 kr, avhengig av hva vi finner» (kunde 3). Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget: 2 500 kr inkludert merverdiavgift. Alle kundene er forbrukere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uforpliktende prisantydning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjengs pris</t>
   </si>
   <si>
     <t xml:space="preserve">Ladeboks med installasjon, inkludert merverdiavgift</t>
@@ -445,6 +526,9 @@
     <t xml:space="preserve">Oppgave 2C: Nordlys: Idas ni tiltak, og tre måter å spørre etisk på</t>
   </si>
   <si>
+    <t xml:space="preserve">Endret siden boka</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ida har laget en liste med ni markedsføringstiltak for Nordlys, fra annonser til konkurranser og et kundekort. Kari vil vite hva som er lovlig etter markedsføringsloven før noe går i trykken. Etterpå diskuterer Kari, Tom og Ida hvorfor de egentlig vil holde seg til loven, og de begrunner det på tre ulike måter.</t>
   </si>
   <si>
@@ -502,9 +586,18 @@
     <t xml:space="preserve">Ida: «Jeg vil være en kalkulatør folk stoler på, så jeg skriver ikke 40 % uten å ha regnet»</t>
   </si>
   <si>
+    <t xml:space="preserve">Pliktetikk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lovens bokstav og lovens ånd: § 3 krever dokumentasjon når annonsen trykkes. Hva krever lovens ånd av Ida før hun skriver «40 %»? Og hva sier det om kjøpsbetingede konkurranser, som loven ikke lenger forbyr? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dydsetikk (sinnelagsetikk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsekvensetikk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fasit, kapittel 20</t>
   </si>
   <si>
@@ -641,9 +734,6 @@
   </si>
   <si>
     <t xml:space="preserve">2A d) Plikten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">§ 7 andre ledd: kontakte forbrukeren når prisen blir betydelig høyere enn hun måtte vente</t>
   </si>
   <si>
     <t xml:space="preserve">2A e) Til kunden og rutinen</t>
@@ -890,7 +980,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -913,6 +1003,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1382,7 +1476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G42"/>
+  <dimension ref="B1:Z42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1390,344 +1484,385 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>560000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="B19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="B20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(20-8),"Riktig.",IF(ABS(C22-(20-1))&lt;=0,"Du har telt fra første arbeidsdag. Fristen er sju dager etter oppstart, så den gikk ut 8. august.",IF(ABS(C22-(20-7))&lt;=0,"Du har trukket fra sju dager, men fristen regnes fra 1. august: 1 + 7 = 8. august. Tell fra den 8.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(ABS(C23-(ROUND(560000/1800,0)))&lt;=1,"Riktig.",IF(ABS(C23-(ROUND(560000/1400,0)))&lt;=1,"Du har delt på fakturerbare timer. Timelønna regnes på alle betalte timer, 1 800.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(560000/1800*1.4,0)))&lt;=1,"Riktig.",IF(ABS(C24-(ROUND(560000/1800*0.4,0)))&lt;=1,"Du har regnet bare tillegget. Overtidslønna er timelønna pluss tillegget: timelønn × 1,40.",IF(ABS(C24-(ROUND(560000/1800,0)))&lt;=1,"Det er vanlig timelønn. Overtid skal ha et tillegg på minst 40 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="B26" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ikke lovlig","Riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den.","Ikke riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Ikke lovlig","Riktig. Overtid skal betales med et tillegg på minst 40 prosent (§ 10-6 ellevte ledd), og avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m).","Ikke riktig. Overtid skal betales med et tillegg på minst 40 prosent (§ 10-6 ellevte ledd), og avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Ikke lovlig","Riktig. Endringer skal inn tidligst mulig og senest den dagen de trer i kraft (§ 14-8). «Innen én måned» er bokas gamle frist, opphevet 1. juli 2024.","Ikke riktig. Endringer skal inn tidligst mulig og senest den dagen de trer i kraft (§ 14-8). «Innen én måned» er bokas gamle frist, opphevet 1. juli 2024."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Lovlig","Riktig. Prøvetid kan avtales skriftlig for inntil seks måneder (§ 15-6 tredje ledd). I prøvetiden er oppsigelsesfristen 14 dager (§ 15-3 sjuende ledd).","Ikke riktig. Prøvetid kan avtales skriftlig for inntil seks måneder (§ 15-6 tredje ledd). I prøvetiden er oppsigelsesfristen 14 dager (§ 15-3 sjuende ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Lovlig","Riktig. Hovedregelen er én måned (§ 15-3 første ledd). Etter fem års ansettelse blir fristen minst to måneder etter loven, uansett hva avtalen sier.","Ikke riktig. Hovedregelen er én måned (§ 15-3 første ledd). Etter fem års ansettelse blir fristen minst to måneder etter loven, uansett hva avtalen sier."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Ikke lovlig","Riktig. Avtalen skal oppgi lønnen ved arbeidsforholdets begynnelse, tillegg, utbetalingsmåte og tidspunkt (§ 14-6 første ledd bokstav i).","Ikke riktig. Avtalen skal oppgi lønnen ved arbeidsforholdets begynnelse, tillegg, utbetalingsmåte og tidspunkt (§ 14-6 første ledd bokstav i)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="20" t="str">
+      <c r="B38" s="21" t="str">
         <f aca="false">IF(LEN(B35)&lt;40,"",IF(AND(ISNUMBER(SEARCH("200",B35)),ISNUMBER(SEARCH("behov",B35))),"Bra: du har med både grensen på 200 timer i 52 uker og at overtid krever et særlig og tidsavgrenset behov. Fast overtid hele året er underbemanning, ikke et tidsavgrenset behov.",IF(OR(ISNUMBER(SEARCH("200",B35)),ISNUMBER(SEARCH("behov",B35))),"Du er på sporet. Ta med både grensen (200 timer i 52 uker uten avtale med tillitsvalgte i tariffbundet virksomhet, § 10-6 fjerde og femte ledd) og vilkåret: overtid krever et særlig og tidsavgrenset behov (§ 10-6 første ledd).","Tips: uten tariffavtale er grensen 200 overtidstimer i 52 uker (§ 10-6 fjerde ledd); 300 krever skriftlig avtale med tillitsvalgte i en tariffbundet virksomhet, og det er Fjell ikke. Overtid krever dessuten et særlig og tidsavgrenset behov (§ 10-6 første ledd). Et helt år med overtid er ikke tidsavgrenset.")))</f>
         <v/>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="18"/>
+      <c r="B39" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="22" t="str">
+      <c r="B40" s="23" t="str">
         <f aca="false">IF(C39="JA","Hint: a: fristen gikk ut 1 + 7 = 8. august; 20 − 8 = 12 dager. b: 560 000 / 1 800 = 311 kr. c: 311,11 × 1,40 = 436 kr. d: 42 timer, overtid uten tillegg, «innen én måned» og «lønn etter avtale» er ikke lovlige; prøvetid seks måneder og én måneds frist er lovlige.","")</f>
         <v/>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="B42" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1822,27 +1957,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Lovlig,Ikke lovlig"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
@@ -1865,7 +2000,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B1:Z39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1873,314 +2008,326 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>54</v>
+      <c r="B11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="23" t="n">
+      <c r="B12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="24" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="23" t="n">
+      <c r="B13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="24" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="23" t="n">
+      <c r="B14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <v>11.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="23" t="n">
+      <c r="B15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="24" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="23" t="n">
+      <c r="B16" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="24" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="23" t="n">
+      <c r="B17" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="24" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="23" t="n">
+      <c r="B18" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="B19" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="25" t="n">
         <f aca="false">SUM(C12:C18)</f>
         <v>52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="B21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="B22" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(2.5+1),"Riktig.",IF(ABS(C24-(2.5))&lt;=0,"Du har bare onsdag (11,5 − 9 = 2,5). Fredag var 10 timer, altså 1 time over.",IF(ABS(C24-(12))&lt;=0,"Det er overtiden for hele uka (52 − 40). Her spør vi bare om timene over 9 i ett døgn.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(52-40),"Riktig.",IF(ABS(C25-(52-40+3.5))&lt;=0,"Du har telt timene over 9 per dag én gang til. De ligger allerede inni de 52 timene. Overtiden er 52 − 40 = 12.",IF(ABS(C25-(52-37.5))&lt;=0,"Du har regnet fra avtalt arbeidstid, 37,5. Lovens overtid regnes fra lovens grense, 40 timer (§ 10-6 andre ledd). Timene mellom 37,5 og 40 er arbeid utover avtalt tid, men ikke overtid etter loven.",IF(ABS(C25-(3.5))&lt;=0,"Det er bare timene over 9 per dag. Uka er på 52 timer, og alt over 40 er overtid.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(52-40-10),"Riktig.",IF(ABS(C26-(12))&lt;=0,"Det er overtiden. Grensen er 10 timer per sju dager; svar hvor mye som ligger over den.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(212-200),"Riktig.",IF(ABS(C27-(212-300))&lt;=0,"Du har brukt 300 timer. Det krever skriftlig avtale med tillitsvalgte i en virksomhet bundet av tariffavtale (§ 10-6 femte ledd). Nordlys har ingen slik avtale, så grensen er 200.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Drøfte behovet for overtid med de tillitsvalgte før den settes i gang (§ 10-6 tredje ledd)","Riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtid gir dessuten minst 40 % tillegg (ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd).","Ikke riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtid gir dessuten minst 40 % tillegg (ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="20" t="str">
+      <c r="B35" s="21" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("200",B32)),ISNUMBER(SEARCH("behov",B32))),"Bra: du har med både at overtid krever et særlig og tidsavgrenset behov, og grensen på 200 timer i 52 uker. Betaling gjør ikke ulovlig overtid lovlig.",IF(OR(ISNUMBER(SEARCH("200",B32)),ISNUMBER(SEARCH("behov",B32))),"Du er på sporet. Ta med både vilkåret (særlig og tidsavgrenset behov, § 10-6 første ledd) og grensen (200 timer i 52 uker uten avtale, fjerde ledd).","Tips: overtid er lov bare når det er et særlig og tidsavgrenset behov (§ 10-6 første ledd). Fast overtid hver uke er underbemanning. Og grensene gjelder uansett lønn: 10 timer per sju dager og 200 timer per 52 uker (fjerde ledd). Arbeidsmiljøet skal være fullt forsvarlig, og arbeidsmengde og tidspress er en del av det psykososiale arbeidsmiljøet (§§ 4-1 og 4-3).")))</f>
         <v/>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="18"/>
+      <c r="B36" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="22" t="str">
+      <c r="B37" s="23" t="str">
         <f aca="false">IF(C36="JA","Hint: a: onsdag 11,5 − 9 = 2,5 og fredag 10 − 9 = 1, til sammen 3,5. b: 52 − 40 = 12 (ikke 12 + 3,5 = 15,5). c: 12 − 10 = 2. d: 212 − 200 = 12.","")</f>
         <v/>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2242,7 +2389,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Drøfte behovet for overtid med de tillitsvalgte før den settes i gang (§ 10-6 tredje ledd),Be montørene jobbe inn timene uten tillegg,Ingenting,så lenge montørene selv vil"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
@@ -2265,7 +2412,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G44"/>
+  <dimension ref="B1:Z44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2273,343 +2420,404 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
+      <c r="B11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>2020</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>2027</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>41</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>2</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>3</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z17" s="0" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="Z18" s="6" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(6),"Riktig.",IF(ABS(C21-(7))&lt;=0,"Fra august 2020 til mars 2027 er det 6 år og 7 måneder. Det sjuende året er ikke fullt før august 2027.",IF(ABS(C21-(5))&lt;=0,"Tell en gang til: august 2020 til august 2026 er seks år, og mars 2027 er etter det.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(2),"Riktig.",IF(ABS(C22-(1))&lt;=0,"Én måned er hovedregelen under fem års ansettelse. Jonas har over fem år: minst to måneder (andre ledd).",IF(ABS(C22-(3))&lt;=0,"Tre måneder gjelder fra ti års sammenhengende ansettelse. Nordlys startet i 2019, så ingen har ti år ennå.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="31. mai","Riktig. Fristen løper fra og med første dag i måneden etter at oppsigelsen fant sted (§ 15-3 fjerde ledd), altså 1. april. April og mai: siste dag er 31. mai. Den vanligste feilen er å telle fra 20. mars.","Ikke riktig. Fristen løper fra og med første dag i måneden etter at oppsigelsen fant sted (§ 15-3 fjerde ledd), altså 1. april. April og mai: siste dag er 31. mai. Den vanligste feilen er å telle fra 20. mars."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="B26" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ja","Riktig. Så langt det er praktisk mulig, med mindre Jonas selv ikke vil. Både grunnlaget og utvelgelsen skal drøftes (§ 15-1).","Ikke riktig. Så langt det er praktisk mulig, med mindre Jonas selv ikke vil. Både grunnlaget og utvelgelsen skal drøftes (§ 15-1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Ja","Riktig. Formkravene i § 15-4. Mangler de, kan oppsigelsen kjennes ugyldig hvis Jonas går til sak innen fire måneder (§ 15-5).","Ikke riktig. Formkravene i § 15-4. Mangler de, kan oppsigelsen kjennes ugyldig hvis Jonas går til sak innen fire måneder (§ 15-5)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Nei","Riktig. Oppsigelse skal skje skriftlig (§ 15-4 første ledd). En muntlig oppsigelse er en formfeil (§ 15-5).","Ikke riktig. Oppsigelse skal skje skriftlig (§ 15-4 første ledd). En muntlig oppsigelse er en formfeil (§ 15-5)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Ja","Riktig. Ved driftsinnskrenkning er oppsigelsen ikke saklig hvis arbeidsgiver har annet passende arbeid å tilby (§ 15-7 andre ledd).","Ikke riktig. Ved driftsinnskrenkning er oppsigelsen ikke saklig hvis arbeidsgiver har annet passende arbeid å tilby (§ 15-7 andre ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Ja","Riktig. Nedbemanning kan være saklig grunn i virksomhetens forhold, men det kreves en bedriftsøkonomisk begrunnelse (boka 20.3.15) og en avveining mellom bedriftens behov og ulempene for den enkelte (§ 15-7 andre ledd).","Ikke riktig. Nedbemanning kan være saklig grunn i virksomhetens forhold, men det kreves en bedriftsøkonomisk begrunnelse (boka 20.3.15) og en avveining mellom bedriftens behov og ulempene for den enkelte (§ 15-7 andre ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Nei","Riktig. Advarsel er sentralt når grunnen er arbeidstakerens forhold. Her er grunnen virksomhetens forhold (boka 20.3.15).","Ikke riktig. Advarsel er sentralt når grunnen er arbeidstakerens forhold. Her er grunnen virksomhetens forhold (boka 20.3.15)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="G34" s="16" t="str">
+      <c r="B34" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="G34" s="17" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="Nei, han kan som hovedregel fortsette i stillingen til saken er avgjort","Riktig. Ved tvist kan arbeidstakeren fortsette i stillingen mens forhandlinger pågår og når søksmål er reist i tide (§ 15-11 første og andre ledd). Vil arbeidsgiver ha ham ut før, må arbeidsgiver kreve det for retten. Er oppsigelsen usaklig, kjennes den ugyldig, og Jonas kan kreve erstatning (§ 15-12).","Ikke riktig. Ved tvist kan arbeidstakeren fortsette i stillingen mens forhandlinger pågår og når søksmål er reist i tide (§ 15-11 første og andre ledd). Vil arbeidsgiver ha ham ut før, må arbeidsgiver kreve det for retten. Er oppsigelsen usaklig, kjennes den ugyldig, og Jonas kan kreve erstatning (§ 15-12)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20" t="str">
+      <c r="B40" s="21" t="str">
         <f aca="false">IF(LEN(B37)&lt;40,"",IF(AND(ISNUMBER(SEARCH("drøft",B37)),ISNUMBER(SEARCH("skriftlig",B37))),"Bra: du har med drøftingen før beslutningen og den skriftlige oppsigelsen. Sjekk at du også har omplassering (§ 15-7 andre ledd) og attesten når han fratrer (§ 15-15).",IF(OR(ISNUMBER(SEARCH("drøft",B37)),ISNUMBER(SEARCH("skriftlig",B37))),"Du har med noe av det. Rekkefølgen er: vurdere annet passende arbeid (§ 15-7), drøftingsmøte med Jonas og den tillitsvalgte (§ 15-1), skriftlig oppsigelse med rettigheter og frister (§ 15-4), attest ved fratreden (§ 15-15).","Tips: først sakligheten: bedriftsøkonomisk begrunnelse, saklig utvelgelse og vurdering av annet passende arbeid (§ 15-7). Så drøftingsmøte med Jonas og den tillitsvalgte før beslutningen (§ 15-1). Så skriftlig oppsigelse levert personlig eller rekommandert, med rett til forhandling, søksmål og å stå i stillingen, og fristene (§ 15-4). Til slutt attest (§ 15-15).")))</f>
         <v/>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="18"/>
+      <c r="B41" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="22" t="str">
+      <c r="B42" s="23" t="str">
         <f aca="false">IF(C41="JA","Hint: a: august 2020 til mars 2027 er 6 år og 7 måneder, altså 6 hele år. b: minst fem år, under ti: to måneder. c: fristen løper fra 1. april; april og mai gir 31. mai. d: ja, ja, nei, ja, ja, nei. e: han kan stå i stillingen (§ 15-11).","")</f>
         <v/>
       </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2712,35 +2920,35 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"20. mai,31. mai,30. april"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$4:$Z$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$6:$Z$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$8:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$10:$Z$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$12:$Z$13</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$14:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Ja,oppsigelsestiden er ute 31. mai,Nei,han kan som hovedregel fortsette i stillingen til saken er avgjort,Nei,en oppsigelse han bestrider er automatisk ugyldig"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41" type="list">
@@ -2763,7 +2971,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B1:Z33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2771,260 +2979,272 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>100</v>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>36000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>42300</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="16" t="str">
+      <c r="B19" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(C19=(36000*1.15),"Riktig.",IF(ABS(C19-(42300*1.15))&lt;=0,"Du har lagt 15 prosent på fakturaen. Prosenten regnes av prisoverslaget.",IF(ABS(C19-(36000*0.15))&lt;=0,"Du har regnet bare tillegget. Taket er overslaget pluss 15 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(ABS(C20-(ROUND((42300-36000)/36000*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C20-(ROUND((42300-36000)/42300*100,1)))&lt;=0.1,"Du har delt på fakturaen. Overskridelsen skal måles mot prisoverslaget, 36 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(42300-36000*1.15),"Riktig.",IF(ABS(C21-(42300-36000))&lt;=0,"Det er hele overskridelsen. Hvor mye av den kunden slipper, avhenger av om overskridelsen var vesentlig og av bruddet på § 7. Det hun i alle fall slipper, er det som ligger over taket.",IF(ABS(C21-(36000*0.15))&lt;=0,"Det er 15 prosent av overslaget, altså rommet opp til taket, ikke det som ligger over.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="§ 7 andre ledd: kontakte forbrukeren når prisen blir betydelig høyere enn hun måtte vente","Riktig. Får tjenesteyteren under utføringen grunn til å anta at prisen blir betydelig høyere enn forbrukeren måtte vente, skal han kontakte forbrukeren (§ 7 andre ledd). Brytes plikten, kan resultatet bli at forbrukeren ikke plikter å betale fullt ut (boka 20.2.2). Arbeidet var fagmessig, og prisen var avtalt som overslag.","Ikke riktig. Får tjenesteyteren under utføringen grunn til å anta at prisen blir betydelig høyere enn forbrukeren måtte vente, skal han kontakte forbrukeren (§ 7 andre ledd). Brytes plikten, kan resultatet bli at forbrukeren ikke plikter å betale fullt ut (boka 20.2.2). Arbeidet var fagmessig, og prisen var avtalt som overslag."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="20" t="str">
+      <c r="B29" s="21" t="str">
         <f aca="false">IF(LEN(B26)&lt;40,"",IF(AND(ISNUMBER(SEARCH("15",B26)),ISNUMBER(SEARCH("kontakt",B26))),"Bra: du har med 15-prosentgrensen og kontakten med kunden underveis. Sjekk at du også sier at 41 400 er et tak, ikke et beløp Nordlys har krav på.",IF(OR(ISNUMBER(SEARCH("15",B26)),ISNUMBER(SEARCH("kontakt",B26))),"Du har med noe av det. Ta med både grensen (ikke vesentlig over overslaget, i alle fall ikke over 15 %, § 32 andre ledd) og rutinen: montøren skal kontakte kunden når prisen løper (§ 7 andre ledd).","Tips: Kari kan ikke kreve mer enn 41 400 kr, og fordi montøren ikke kontaktet kunden (§ 7 andre ledd), kan kunden slippe å betale fullt ut. Rutinen: skriftlig prisform i tilbudsmalen, og én telefon til kunden når montøren ser at timene løper, notert på arbeidsordren.")))</f>
         <v/>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="18"/>
+      <c r="B30" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="str">
+      <c r="B31" s="23" t="str">
         <f aca="false">IF(C30="JA","Hint: a: 36 000 × 1,15 = 41 400. b: 42 300 − 36 000 = 6 300; 6 300 / 36 000 = 17,5 %. c: 42 300 − 41 400 = 900. d: § 7 andre ledd.","")</f>
         <v/>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="B33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3078,7 +3298,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"§ 5 første ledd: utføre tjenesten fagmessig,§ 7 andre ledd: kontakte forbrukeren når prisen blir betydelig høyere enn hun måtte vente,§ 32 første ledd: ta gjengs pris"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
@@ -3101,7 +3321,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G42"/>
+  <dimension ref="B1:Z42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3109,317 +3329,427 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>100</v>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>15300</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>2500</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>15</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z15" s="0" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="Z16" s="6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="Z17" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z18" s="0" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="16" t="str">
+      <c r="B19" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(C19=(15300*1.15),"Riktig.",IF(ABS(C19-(15300))&lt;=0,"Det er overslaget. Et prisoverslag kan overskrides noe, men ikke vesentlig, og i alle fall ikke med mer enn 15 prosent.",IF(ABS(C19-(15300*0.15))&lt;=0,"Du har regnet bare tillegget. Taket er overslaget pluss 15 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Kontakte kunden før han gjør tilleggsarbeidet (§ 9 første ledd)","Riktig. Viser det seg behov for arbeid utenfor oppdraget som er praktisk å utføre sammen med oppdraget, skal tjenesteyteren kontakte forbrukeren (§ 9 første ledd). Bare tilleggsarbeid som ikke kan utsettes uten fare for vesentlig skade, skal gjøres i rimelig utstrekning uten videre (§ 9 tredje ledd). Fast pris gjelder det avtalte oppdraget, ikke arbeid utenfor det.","Ikke riktig. Viser det seg behov for arbeid utenfor oppdraget som er praktisk å utføre sammen med oppdraget, skal tjenesteyteren kontakte forbrukeren (§ 9 første ledd). Bare tilleggsarbeid som ikke kan utsettes uten fare for vesentlig skade, skal gjøres i rimelig utstrekning uten videre (§ 9 tredje ledd). Fast pris gjelder det avtalte oppdraget, ikke arbeid utenfor det."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z22" s="0" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="16" t="str">
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(15300+2500),"Riktig.",IF(ABS(C23-(15300*1.15+2500))&lt;=0,"Du har lagt 15 prosent på en fast pris. Fast pris er fast; 15 prosent gjelder bare prisoverslag.",IF(ABS(C23-(15300))&lt;=0,"Du har glemt tilleggsarbeidet. Tilleggsarbeid som er avtalt etter § 9, kan kreves betalt (§ 33).","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z24" s="0" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Nei, 15 % er et tak; prisen skal ikke overstige overslaget vesentlig, og overskridelsen må kunne begrunnes","Riktig. Prisen skal ikke overstige overslaget vesentlig, og i alle fall ikke med mer enn 15 prosent (§ 32 andre ledd). 15 prosent er yttergrensen, ikke et fribeløp. Et overslag er heller ikke en fast pris; det kan overskrides noe når det er grunn til det (boka 20.2.4).","Ikke riktig. Prisen skal ikke overstige overslaget vesentlig, og i alle fall ikke med mer enn 15 prosent (§ 32 andre ledd). 15 prosent er yttergrensen, ikke et fribeløp. Et overslag er heller ikke en fast pris; det kan overskrides noe når det er grunn til det (boka 20.2.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z26" s="0" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="B27" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="Z27" s="6" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Fast pris","Riktig. Bindende fast pris: aldri mer for det avtalte oppdraget. Tilleggsarbeid utenfor oppdraget kommer i tillegg (§ 33).","Ikke riktig. Bindende fast pris: aldri mer for det avtalte oppdraget. Tilleggsarbeid utenfor oppdraget kommer i tillegg (§ 33)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Prisoverslag","Riktig. Prisen skal ikke overstige overslaget vesentlig, og i alle fall ikke med mer enn 15 prosent (§ 32 andre ledd).","Ikke riktig. Prisen skal ikke overstige overslaget vesentlig, og i alle fall ikke med mer enn 15 prosent (§ 32 andre ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Uforpliktende prisantydning","Riktig. Den friest formulerte prisformen. Da gjelder gjengs pris, så lenge den ikke er urimelig (§ 32 første ledd). Det er håndverkeren som må godtgjøre hvilken prisform som ble gitt.","Ikke riktig. Den friest formulerte prisformen. Da gjelder gjengs pris, så lenge den ikke er urimelig (§ 32 første ledd). Det er håndverkeren som må godtgjøre hvilken prisform som ble gitt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z30" s="6" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Høyeste pris","Riktig. Høyeste pris kan bli lavere, aldri høyere (boka 20.2.4).","Ikke riktig. Høyeste pris kan bli lavere, aldri høyere (boka 20.2.4)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z31" s="6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Gjengs pris","Riktig. Er prisen ikke avtalt, skal den regnes ut på vanlig måte for tilsvarende tjenester på avtaletiden, gjengs pris, dersom den ikke er urimelig (§ 32 første ledd).","Ikke riktig. Er prisen ikke avtalt, skal den regnes ut på vanlig måte for tilsvarende tjenester på avtaletiden, gjengs pris, dersom den ikke er urimelig (§ 32 første ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="20" t="str">
+      <c r="B38" s="21" t="str">
         <f aca="false">IF(LEN(B35)&lt;40,"",IF(AND(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Bra: du velger fast pris og sier at den skal stå skriftlig. Si også hva som ikke er med i prisen, og at slikt avtales med kunden før det gjøres (§ 9).",IF(OR(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Du er på sporet. En standardpakke med kjent tidsbruk passer for fast pris, og prisformen må stå skriftlig med ord, fordi det er håndverkeren som må godtgjøre hva som ble lovet.","Tips: en standardpakke med kjent tidsbruk passer for fast pris: kunden vet hva hun får, og Fjell bærer risikoen for tiden. Skriv «fast pris, inkludert merverdiavgift» med ord, og si hva som ikke er med (nytt vern, ny kurs) og at det avtales med kunden før det gjøres (§ 9). «Ca. 15 000» bør ut av malen.")))</f>
         <v/>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="18"/>
+      <c r="B39" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="22" t="str">
+      <c r="B40" s="23" t="str">
         <f aca="false">IF(C39="JA","Hint: a: 15 300 × 1,15 = 17 595. b: kontakt kunden først (§ 9 første ledd). c: 15 300 + 2 500 = 17 800. d: nei, 15 % er et tak. e: fast pris, prisoverslag, uforpliktende prisantydning, høyeste pris, gjengs pris.","")</f>
         <v/>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="B42" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3514,31 +3844,31 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Montere vernet og legge det på fakturaen; det er praktisk å gjøre samtidig,Kontakte kunden før han gjør tilleggsarbeidet (§ 9 første ledd),Ingenting; fast pris betyr at alt nødvendig arbeid er inkludert"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Ja,15 % over overslaget er alltid lov,Nei,15 % er et tak; prisen skal ikke overstige overslaget vesentlig,og overskridelsen må kunne begrunnes,Nei,et prisoverslag er det samme som fast pris"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Fast pris,Høyeste pris,Prisoverslag,Uforpliktende prisantydning,Gjengs pris"</formula1>
+      <formula1>$Z$7:$Z$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Fast pris,Høyeste pris,Prisoverslag,Uforpliktende prisantydning,Gjengs pris"</formula1>
+      <formula1>$Z$12:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Fast pris,Høyeste pris,Prisoverslag,Uforpliktende prisantydning,Gjengs pris"</formula1>
+      <formula1>$Z$17:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Fast pris,Høyeste pris,Prisoverslag,Uforpliktende prisantydning,Gjengs pris"</formula1>
+      <formula1>$Z$22:$Z$26</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Fast pris,Høyeste pris,Prisoverslag,Uforpliktende prisantydning,Gjengs pris"</formula1>
+      <formula1>$Z$27:$Z$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
@@ -3561,7 +3891,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G37"/>
+  <dimension ref="B1:Z37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3569,309 +3899,430 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="B12" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="Z12" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="G13" s="16" t="str">
+      <c r="B13" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="G13" s="17" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Ikke lovlig","Riktig. Påstander om virkninger skal kunne dokumenteres, og dokumentasjonen skal foreligge i det øyeblikket markedsføringen skjer (§ 3, boka 20.1.1).","Ikke riktig. Påstander om virkninger skal kunne dokumenteres, og dokumentasjonen skal foreligge i det øyeblikket markedsføringen skjer (§ 3, boka 20.1.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="G14" s="16" t="str">
+      <c r="B14" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="G14" s="17" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Lovlig","Riktig. Åpenbare overdrivelser er tillatt; folk flest tar dem for hva de er (§ 3, bokas «verdens beste kjøttboller»).","Ikke riktig. Åpenbare overdrivelser er tillatt; folk flest tar dem for hva de er (§ 3, bokas «verdens beste kjøttboller»)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="G15" s="16" t="str">
+      <c r="B15" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="G15" s="17" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Lovlig","Riktig. Forbudet mot utlodninger er opphevet, og vilkårene er klare og lett tilgjengelige (§ 18, boka 20.1.3).","Ikke riktig. Forbudet mot utlodninger er opphevet, og vilkårene er klare og lett tilgjengelige (§ 18, boka 20.1.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="G16" s="16" t="str">
+      <c r="B16" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="G16" s="17" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Endret siden boka","Riktig. Boka: forbudt å gjøre deltakelse betinget av kjøp (§ 18 slik den lød i 2009). Loven i dag: § 18 ble endret i 2013 og krever bare klare og lett tilgjengelige vilkår; kjøpsbetingede konkurranser er ikke forbudt i seg selv, men vurderes etter §§ 6–9. I en besvarelse: svar etter boka, og nevn endringen.","Ikke riktig. Boka: forbudt å gjøre deltakelse betinget av kjøp (§ 18 slik den lød i 2009). Loven i dag: § 18 ble endret i 2013 og krever bare klare og lett tilgjengelige vilkår; kjøpsbetingede konkurranser er ikke forbudt i seg selv, men vurderes etter §§ 6–9. I en besvarelse: svar etter boka, og nevn endringen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="G17" s="16" t="str">
+      <c r="B17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="G17" s="17" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Ikke lovlig","Riktig. Press ut fra en maktposisjon som begrenser forbrukerens handlefrihet, selv uten trusler, er aggressiv handelspraksis (§ 9, boka 20.1.2).","Ikke riktig. Press ut fra en maktposisjon som begrenser forbrukerens handlefrihet, selv uten trusler, er aggressiv handelspraksis (§ 9, boka 20.1.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="18"/>
-      <c r="G18" s="16" t="str">
+      <c r="B18" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="G18" s="17" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Ikke lovlig","Riktig. Uriktige opplysninger som er egnet til å påvirke kjøpsbeslutningen, er villedende handlinger (§ 7).","Ikke riktig. Uriktige opplysninger som er egnet til å påvirke kjøpsbeslutningen, er villedende handlinger (§ 7)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="G19" s="16" t="str">
+      <c r="B19" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Ikke lovlig","Riktig. Vesentlige opplysninger gitt på en uklar eller uhensiktsmessig måte er villedende utelatelse (§ 8).","Ikke riktig. Vesentlige opplysninger gitt på en uklar eller uhensiktsmessig måte er villedende utelatelse (§ 8)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Ikke lovlig","Riktig. Markedsføring skal utformes slik at forbrukerne lett ser at det er markedsføring (§ 3, boka 20.1.1).","Ikke riktig. Markedsføring skal utformes slik at forbrukerne lett ser at det er markedsføring (§ 3, boka 20.1.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Lovlig","Riktig. Et samlemerke som gir mer av den samme ytelsen er tillatt; vilkårene skal stå klart (§ 18, bokas bilvaskeksempel).","Ikke riktig. Et samlemerke som gir mer av den samme ytelsen er tillatt; vilkårene skal stå klart (§ 18, bokas bilvaskeksempel)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z22" s="0" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="B23" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="Z23" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="B24" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="Z24" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Pliktetikk","Riktig. Handlingen vurderes i seg selv, som en regel som kan gjelde for alle: Kants kategoriske imperativ (boka 20.5.1).","Ikke riktig. Handlingen vurderes i seg selv, som en regel som kan gjelde for alle: Kants kategoriske imperativ (boka 20.5.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Konsekvensetikk","Riktig. Handlingen vurderes etter resultatet. Svakheten: målet kan hellige middelet (boka 20.5.3).","Ikke riktig. Handlingen vurderes etter resultatet. Svakheten: målet kan hellige middelet (boka 20.5.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Dydsetikk (sinnelagsetikk)","Riktig. Handlingen springer ut av karakteregenskapene til den som handler; dyd betyr å duge (boka 20.5.2, kalt sinnelagsetikk i 20.6).","Ikke riktig. Handlingen springer ut av karakteregenskapene til den som handler; dyd betyr å duge (boka 20.5.2, kalt sinnelagsetikk i 20.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z28" s="0" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="B29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="Z29" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="Z30" s="6" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="Z31" s="6" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="Z32" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="20" t="str">
+      <c r="B33" s="21" t="str">
         <f aca="false">IF(LEN(B30)&lt;40,"",IF(AND(ISNUMBER(SEARCH("ånd",B30)),ISNUMBER(SEARCH("dokument",B30))),"Bra: du bruker lovens ånd og dokumentasjonen. Sjekk at du også sier at det som er lovlig etter bokstaven (kjøpsbetinget konkurranse) likevel kan vurderes etter ånden: får kunden tenke fritt?",IF(OR(ISNUMBER(SEARCH("ånd",B30)),ISNUMBER(SEARCH("dokument",B30))),"Du er på sporet. Lovens ånd er det loven skulle oppnå: at kunden kan stole på det som påstås, og velge fritt. Den krever mer av Ida enn bokstaven, aldri mindre (boka 20.6).","Tips: bokstaven krever at dokumentasjonen finnes når annonsen trykkes (§ 3). Ånden krever at Ida faktisk tror på tallet og kan forklare det til en kunde. Kjøpsbetingede konkurranser er ikke lenger forbudt i seg selv, men ånden spør likevel om kunden kjøper for å vinne i stedet for fordi hun trenger jobben (boka 20.6).")))</f>
         <v/>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="Z33" s="6" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="18"/>
+      <c r="B34" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="Z34" s="6" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="22" t="str">
+      <c r="B35" s="23" t="str">
         <f aca="false">IF(C34="JA","Hint: Lovlig: slagordet, trekningen blant alle som ber om befaring, samlemerket. Ikke lovlig: 40 %-annonsen (§ 3), strømmen som holdes tilbake (§ 9), «Godkjent av» (§ 7), liten skrift (§ 8), reklamen som nyhetsartikkel (§ 3). Endret siden boka: trekningen som krever kjøp (§ 18, endret 2013). Etikk: Kari pliktetikk, Tom konsekvensetikk, Ida dydsetikk.","")</f>
         <v/>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="Z35" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z36" s="0" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="B37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3990,51 +4441,51 @@
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Lovlig,Ikke lovlig,Endret siden boka"</formula1>
+      <formula1>$Z$25:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Pliktetikk,Dydsetikk (sinnelagsetikk),Konsekvensetikk"</formula1>
+      <formula1>$Z$28:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Pliktetikk,Dydsetikk (sinnelagsetikk),Konsekvensetikk"</formula1>
+      <formula1>$Z$31:$Z$33</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Pliktetikk,Dydsetikk (sinnelagsetikk),Konsekvensetikk"</formula1>
+      <formula1>$Z$34:$Z$36</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
@@ -4067,333 +4518,333 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="s">
-        <v>152</v>
+      <c r="B2" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>156</v>
+      <c r="B5" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="29" t="n">
+      <c r="B6" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>158</v>
+      <c r="D6" s="29" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="29" t="n">
+      <c r="B7" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="30" t="n">
         <v>311</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>160</v>
+      <c r="D7" s="29" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="29" t="n">
+      <c r="B8" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="30" t="n">
         <v>436</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>162</v>
+      <c r="D8" s="29" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="28" t="s">
-        <v>164</v>
+      <c r="B9" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="29" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="28" t="s">
-        <v>166</v>
+      <c r="B10" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="29" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="29" t="n">
+      <c r="B11" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="30" t="n">
         <v>3.5</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>168</v>
+      <c r="D11" s="29" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="29" t="n">
+      <c r="B12" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>170</v>
+      <c r="D12" s="29" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="29" t="n">
+      <c r="B13" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>172</v>
+      <c r="D13" s="29" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="29" t="n">
+      <c r="B14" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>174</v>
+      <c r="D14" s="29" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="28" t="s">
-        <v>176</v>
+      <c r="B15" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="29" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="28" t="s">
-        <v>178</v>
+      <c r="B16" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="29" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="29" t="n">
+      <c r="B17" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>180</v>
+      <c r="D17" s="29" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="29" t="n">
+      <c r="B18" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>182</v>
+      <c r="D18" s="29" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="28" t="s">
-        <v>184</v>
+      <c r="B19" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="29" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="28" t="s">
-        <v>186</v>
+      <c r="B20" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="29" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="28" t="s">
-        <v>188</v>
+      <c r="B21" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="29" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="28" t="s">
-        <v>190</v>
+      <c r="B22" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="29" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="29" t="n">
+      <c r="B23" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" s="30" t="n">
         <v>41400</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>192</v>
+      <c r="D23" s="29" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="29" t="n">
+      <c r="B24" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" s="30" t="n">
         <v>17.5</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>194</v>
+      <c r="D24" s="29" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="29" t="n">
+      <c r="B25" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" s="30" t="n">
         <v>900</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>196</v>
+      <c r="D25" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="28" t="s">
-        <v>198</v>
+      <c r="B26" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="28" t="s">
-        <v>200</v>
+      <c r="B27" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" s="29" t="n">
+      <c r="B28" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="30" t="n">
         <v>17595</v>
       </c>
-      <c r="D28" s="28" t="s">
-        <v>202</v>
+      <c r="D28" s="29" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="28" t="s">
-        <v>204</v>
+      <c r="B29" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="29" t="n">
+      <c r="B30" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="30" t="n">
         <v>17800</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>206</v>
+      <c r="D30" s="29" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="28" t="s">
-        <v>208</v>
+      <c r="B31" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="29" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="28" t="s">
-        <v>210</v>
+      <c r="B32" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="29" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="28" t="s">
-        <v>212</v>
+      <c r="B33" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="29" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="28" t="s">
-        <v>214</v>
+      <c r="B34" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="29" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="28" t="s">
-        <v>216</v>
+      <c r="B35" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="29" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="28" t="s">
-        <v>218</v>
+      <c r="B36" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="29" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
+++ b/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="252">
   <si>
     <t xml:space="preserve">Noen viktige lover: oppgaver til kapittel 20</t>
   </si>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro ansetter en tredje montør, fast, fra 1. august. Mona har skrevet arbeidsavtalen selv etter en gammel mal fra en bekjent, og den ble signert 20. august. Montøren får samme lønn som de to andre: 560 000 kr i året for 1 800 betalte timer. Fjell er ikke bundet av tariffavtale. Mona spør deg om avtalen holder, og om hun kan la de to montørene ta 300 overtidstimer hver i stedet for å ansette den tredje.</t>
+    <t xml:space="preserve">Fjell Elektro ansetter en tredje montør, fast, fra 1. august. Mona har skrevet arbeidsavtalen selv etter en gammel mal fra en bekjent, og den ble signert 20. august. Montøren får samme lønn som de to andre: 560 000 kr i året for 1 800 betalte timer. Fjell er ikke bundet av tariffavtale, men allmenngjøringen av Landsoverenskomsten for elektrofagene gjelder likevel. Mona spør deg om avtalen holder, og om hun kan la de to montørene ta 300 overtidstimer hver i stedet for å ansette den tredje.</t>
   </si>
   <si>
     <t xml:space="preserve">Begrepene du trenger</t>
   </si>
   <si>
-    <t xml:space="preserve">Arbeidsmiljøloven er et minstekrav: en avtale kan gi bedre vilkår enn loven, aldri svakere. Skriftlig arbeidsavtale senest sju dager etter oppstart (§ 14-5). Endringer inn i avtalen senest den dagen de trer i kraft (§ 14-8). Alminnelig arbeidstid høyst 9 timer i døgnet og 40 i uka (§ 10-4). Overtid krever et særlig og tidsavgrenset behov, høyst 200 timer i 52 uker uten avtale, og minst 40 % tillegg (§ 10-6).</t>
+    <t xml:space="preserve">Arbeidsmiljøloven er et minstekrav: en avtale kan gi bedre vilkår enn loven, aldri svakere. Skriftlig arbeidsavtale senest sju dager etter oppstart (§ 14-5). Endringer inn i avtalen senest den dagen de trer i kraft (§ 14-8). Alminnelig arbeidstid høyst 9 timer i døgnet og 40 i uka (§ 10-4). Overtid krever et særlig og tidsavgrenset behov og høyst 200 timer i 52 uker uten avtale (§ 10-6). Loven krever minst 40 % tillegg; i elektrofagene gir allmenngjøringen av Landsoverenskomsten 37,5 timers uke og 50 % tillegg, også uten tariffavtale.</t>
   </si>
   <si>
     <t xml:space="preserve">Tallene</t>
   </si>
   <si>
-    <t xml:space="preserve">Montøren begynte 1. august. Arbeidsavtalen ble signert 20. august. Loven krever skriftlig avtale senest sju dager etter at arbeidsforholdet begynte (arbeidsmiljøloven § 14-5 andre ledd), altså senest 8. august. Lønn 560 000 kr i året for 1 800 betalte timer. Overtid skal lønnes med et tillegg på minst 40 prosent (§ 10-6 ellevte ledd).</t>
+    <t xml:space="preserve">Montøren begynte 1. august. Arbeidsavtalen ble signert 20. august. Loven krever skriftlig avtale senest sju dager etter at arbeidsforholdet begynte (arbeidsmiljøloven § 14-5 andre ledd), altså senest 8. august. Lønn 560 000 kr i året for 1 800 betalte timer. Loven krever et overtidstillegg på minst 40 prosent (§ 10-6 ellevte ledd), men Fjell er elektrobedrift: forskriften om allmenngjøring av Landsoverenskomsten for elektrofagene gjelder også uten tariffavtale, og den gir 37,5 timers ordinær arbeidsuke og 50 prosent overtidstillegg (100 prosent etter klokka 21 og på søn- og helligdager).</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">Betalte timer i året</t>
   </si>
   <si>
-    <t xml:space="preserve">Minste overtidstillegg, prosent (§ 10-6)</t>
+    <t xml:space="preserve">Overtidstillegg i elektrofagene, prosent (allmenngjøringen)</t>
   </si>
   <si>
     <t xml:space="preserve">Oppgaven, trinn for trinn</t>
@@ -136,7 +136,7 @@
   <si>
     <t xml:space="preserve">1. Regn hvor mange dager for sent avtalen ble signert: fristen gikk ut 1 + 7 = 8. august.
 2. Regn timelønna: årslønn delt på betalte timer. Hele kroner.
-3. Regn hva en overtidstime minst skal koste Fjell: timelønn ganger 1,40. Hele kroner.
+3. Regn hva en overtidstime på dagtid minst skal koste Fjell i lønn: timelønn ganger 1,50. Hele kroner.
 4. Gå gjennom seks punkter i Monas utkast og velg Lovlig eller Ikke lovlig. Sjekken forklarer med paragraf.
 5. Skriv svaret til Mona i e.</t>
   </si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">kr per time</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Minste overtidslønn per time: timelønn × 1,40 (§ 10-6 ellevte ledd)</t>
+    <t xml:space="preserve">c) Minste overtidslønn per time på dagtid: timelønn × 1,50 (allmenngjøringen for elektrofagene)</t>
   </si>
   <si>
     <t xml:space="preserve">d) Punktene i Monas utkast til arbeidsavtale: velg Lovlig eller Ikke lovlig</t>
@@ -198,13 +198,13 @@
     <t xml:space="preserve">Ingenting, så lenge montørene selv vil</t>
   </si>
   <si>
-    <t xml:space="preserve">Ronny er formann på nybygg hos Nordlys. Laget hans hadde en travel uke: 7,5, 9, 11,5, 8, 10, 6 og 0 timer. Kari har også sett at en montør i laget har 212 overtidstimer de siste 52 ukene, og hun sier: «Så lenge de får betalt, er det vel greit?» Nordlys har avtalt 37,5 timers uke og har ingen avtale med tillitsvalgte om utvidet overtid.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alminnelig arbeidstid: høyst 9 timer i døgnet og 40 timer i uka (§ 10-4). Overtid er arbeid utover lovens grense (§ 10-6 andre ledd) og krever et særlig og tidsavgrenset behov (første ledd). Uten avtale: høyst 10 timer per sju dager, 25 per fire uker og 200 per 52 uker (fjerde ledd). Samlet arbeidstid høyst 13 timer i døgnet (åttende ledd). Tillegg minst 40 % (ellevte ledd).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronnys lag hadde en travel uke på et nybygg. Timene per dag står i tabellen; arket summerer dem. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (arbeidsmiljøloven § 10-4 første ledd). Alt over lovens grense er overtid (§ 10-6 andre ledd). Uten skriftlig avtale med tillitsvalgte er overtid begrenset til 10 timer per sju dager, 25 timer per fire uker og 200 timer per 52 uker (§ 10-6 fjerde ledd). Nordlys har avtalt 37,5 timers uke, men ingen avtale om utvidet overtid. En montør i laget har 212 overtidstimer de siste 52 ukene.</t>
+    <t xml:space="preserve">Ronny er formann på nybygg hos Nordlys. Laget hans hadde en travel uke: 7,5, 9, 11,5, 8, 10, 6 og 0 timer. Kari har også sett at en montør i laget har 212 overtidstimer de siste 52 ukene, og hun sier: «Så lenge de får betalt, er det vel greit?» Nordlys er bundet av Landsoverenskomsten for elektrofagene, med 37,5 timers ordinær arbeidsuke, og har ingen avtale med tillitsvalgte om utvidet overtid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alminnelig arbeidstid: høyst 9 timer i døgnet og 40 timer i uka (§ 10-4). Lovens overtid er arbeid utover lovens grense (§ 10-6 andre ledd) og krever et særlig og tidsavgrenset behov (første ledd). Uten avtale: høyst 10 timer per sju dager, 25 per fire uker og 200 per 52 uker (fjerde ledd). Samlet arbeidstid høyst 13 timer i døgnet (åttende ledd). Betalingen: Landsoverenskomsten for elektrofagene regner alt over 37,5 timer som overtid, med 50 % tillegg og 100 % etter klokka 21, på søn- og helligdager og på fri lørdag (loven: minst 40 %).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronnys lag hadde en travel uke på et nybygg. Timene per dag står i tabellen; arket summerer dem. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (arbeidsmiljøloven § 10-4 første ledd). Uten skriftlig avtale med tillitsvalgte er overtid begrenset til 10 timer per sju dager, 25 timer per fire uker og 200 timer per 52 uker (§ 10-6 fjerde ledd); de grensene telles fra lovens 40 timer. Betalingen følger tariffavtalen: Nordlys er bundet av Landsoverenskomsten for elektrofagene, der ordinær arbeidstid er 37,5 timer og alt arbeid utover det er overtid med 50 % tillegg (100 % etter klokka 21, på søn- og helligdager og på lørdager når bedriften har fri hver lørdag, som Nordlys har). Nordlys har ingen avtale om utvidet overtid. En montør i laget har 212 overtidstimer de siste 52 ukene.</t>
   </si>
   <si>
     <t xml:space="preserve">Dag</t>
@@ -238,10 +238,11 @@
   </si>
   <si>
     <t xml:space="preserve">1. Finn timene over 9 i ett døgn, og legg dem sammen.
-2. Regn overtiden for uka etter loven: timer utover 40. Timene over 9 per dag ligger allerede inni det tallet; tell dem ikke to ganger.
+2. Regn overtiden for uka etter lovens grenser: timer utover 40. Timene over 9 per dag ligger allerede inni det tallet; tell dem ikke to ganger.
 3. Sammenlikn med grensen på 10 overtidstimer per sju dager.
 4. Regn hvor mange timer montøren med 212 timer ligger over årsgrensen.
-5. Velg hva Ronny skal gjøre før neste travle uke, og skriv forklaringen til Kari.</t>
+5. Regn hvor mange timer Nordlys skal betale overtidstillegg for etter tariffavtalen: alt over 37,5 timer.
+6. Velg hva Ronny skal gjøre før neste travle uke, og skriv forklaringen til Kari.</t>
   </si>
   <si>
     <t xml:space="preserve">a) Timer over 9 i ett døgn, lagt sammen for uka (onsdag og fredag)</t>
@@ -250,7 +251,7 @@
     <t xml:space="preserve">timer</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Overtid i uka etter loven: timer utover 40</t>
+    <t xml:space="preserve">b) Overtid i uka etter lovens grenser: timer utover 40</t>
   </si>
   <si>
     <t xml:space="preserve">c) Hvor mange timer over grensen på 10 overtidstimer per sju dager?</t>
@@ -259,10 +260,13 @@
     <t xml:space="preserve">d) Montøren med 212 overtidstimer: hvor mange timer over årsgrensen uten avtale?</t>
   </si>
   <si>
-    <t xml:space="preserve">e) Hva skal Ronny gjøre før neste travle uke?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f) Kari sier: «Så lenge montørene får betalt, er det vel greit?» Forklar henne hvorfor det ikke holder. Bruk vilkåret for overtid og årsgrensen. To–tre setninger.</t>
+    <t xml:space="preserve">e) Timer med overtidstillegg etter Landsoverenskomsten for elektrofagene: alt over 37,5 timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f) Hva skal Ronny gjøre før neste travle uke?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g) Kari sier: «Så lenge montørene får betalt, er det vel greit?» Forklar henne hvorfor det ikke holder. Bruk vilkåret for overtid og årsgrensen. To–tre setninger.</t>
   </si>
   <si>
     <t xml:space="preserve">20. mai</t>
@@ -429,7 +433,7 @@
     <t xml:space="preserve">e) Kunden sier: «Jeg betaler 36 000, ikke en krone mer.» Hva svarer Kari, og hvilken rutine innfører hun så det ikke skjer igjen? Tre setninger med paragraf.</t>
   </si>
   <si>
-    <t xml:space="preserve">Montere vernet og legge det på fakturaen; det er praktisk å gjøre samtidig</t>
+    <t xml:space="preserve">Montere underfordelingen og legge den på fakturaen; det er praktisk å gjøre samtidig</t>
   </si>
   <si>
     <t xml:space="preserve">Oppgave 2B: Fjell Elektro: tre måter å si prisen på</t>
@@ -444,7 +448,7 @@
     <t xml:space="preserve">Ja, 15 % over overslaget er alltid lov</t>
   </si>
   <si>
-    <t xml:space="preserve">Mona selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift og har brukt tre ulike formuleringer om prisen i tilbudene. Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget, 2 500 kr. Mona spør hva hun kan fakturere, og hva tilbudsmalen bør si.</t>
+    <t xml:space="preserve">Mona selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift og har brukt tre ulike formuleringer om prisen i tilbudene. Hos kunde 1 finner montøren at sikringsskapet er fullt, og en ny underfordeling må monteres, utenfor oppdraget, 5 000 kr. Mona spør hva hun kan fakturere, og hva tilbudsmalen bør si.</t>
   </si>
   <si>
     <t xml:space="preserve">Nei, 15 % er et tak; prisen skal ikke overstige overslaget vesentlig, og overskridelsen må kunne begrunnes</t>
@@ -465,7 +469,7 @@
     <t xml:space="preserve">Prisoverslag</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift. Mona har brukt tre formuleringer i tilbudene: «fast pris 15 300 kr» (kunde 1), «prisoverslag 15 300 kr» (kunde 2) og «ca. 15 000 kr, avhengig av hva vi finner» (kunde 3). Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget: 2 500 kr inkludert merverdiavgift. Alle kundene er forbrukere.</t>
+    <t xml:space="preserve">Fjell Elektro selger «ladeboks med installasjon» for 15 300 kr inkludert merverdiavgift. Mona har brukt tre formuleringer i tilbudene: «fast pris 15 300 kr» (kunde 1), «prisoverslag 15 300 kr» (kunde 2) og «ca. 15 000 kr, avhengig av hva vi finner» (kunde 3). Hos kunde 1 finner montøren at sikringsskapet er fullt, og en ny underfordeling må monteres, utenfor oppdraget: 5 000 kr inkludert merverdiavgift. Alle kundene er forbrukere.</t>
   </si>
   <si>
     <t xml:space="preserve">Uforpliktende prisantydning</t>
@@ -477,14 +481,14 @@
     <t xml:space="preserve">Ladeboks med installasjon, inkludert merverdiavgift</t>
   </si>
   <si>
-    <t xml:space="preserve">Nytt vern utenfor oppdraget (tilleggsarbeid), inkludert merverdiavgift</t>
+    <t xml:space="preserve">Ny underfordeling utenfor oppdraget (tilleggsarbeid), inkludert merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Høyeste overskridelse av et prisoverslag, prosent (§ 32 andre ledd)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Regn taket for kunde 2, som fikk prisoverslag.
-2. Velg hva montøren skal gjøre først hos kunde 1 når han finner vernet.
+2. Velg hva montøren skal gjøre først hos kunde 1 når han ser at skapet er fullt.
 3. Kunde 1 sier ja på telefon. Regn hva Fjell kan fakturere i alt.
 4. Ta stilling til om 15 prosent er et fribeløp.
 5. Sorter fem prisformuleringer til riktig prisform, og skriv hva tilbudsmalen bør si.</t>
@@ -493,10 +497,10 @@
     <t xml:space="preserve">a) Kunde 2 fikk prisoverslag på 15 300 kr. Det høyeste Fjell kan fakturere for oppdraget</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Hos kunde 1 finner montøren at laderen trenger et nytt vern, utenfor oppdraget. Det er praktisk å gjøre det nå. Hva først?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c) Kunde 1 sier ja til vernet på telefon. Hva kan Fjell fakturere i alt? Fast pris pluss tilleggsarbeidet</t>
+    <t xml:space="preserve">b) Hos kunde 1 finner montøren at sikringsskapet er fullt, og en ny underfordeling må monteres, utenfor oppdraget. Det er praktisk å gjøre det nå. Hva først?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c) Kunde 1 sier ja til underfordelingen på telefon. Hva kan Fjell fakturere i alt? Fast pris pluss tilleggsarbeidet</t>
   </si>
   <si>
     <t xml:space="preserve">d) Hos kunde 2 tok jobben lengre tid enn Mona regnet med, uten at noe uforutsett dukket opp. Kan Fjell fakturere 17 595 kr «fordi det er innenfor 15 %»?</t>
@@ -628,13 +632,13 @@
     <t xml:space="preserve">1A c) Overtidslønn per time, minst</t>
   </si>
   <si>
-    <t xml:space="preserve">311,11 × 1,40 = 435,56, avrundet 436 kr (§ 10-6 ellevte ledd: tillegg minst 40 %). En tariffavtale kan gi mer, aldri mindre</t>
+    <t xml:space="preserve">311,11 × 1,50 = 466,67, avrundet 467 kr. Loven krever minst 40 % (§ 10-6 ellevte ledd), men allmenngjøringen av Landsoverenskomsten for elektrofagene gir 50 % på dagtid og 100 % etter klokka 21 og på søn- og helligdager, også for Fjell uten tariffavtale</t>
   </si>
   <si>
     <t xml:space="preserve">1A d) Monas utkast</t>
   </si>
   <si>
-    <t xml:space="preserve">Ikke lovlig: 42 timer (§ 10-4), overtid uten tillegg (§ 10-6), endringer innen én måned (§ 14-8), lønn uten beløp (§ 14-6). Lovlig: prøvetid seks måneder (§ 15-6), gjensidig frist én måned (§ 15-3)</t>
+    <t xml:space="preserve">Ikke lovlig: 42 timer (§ 10-4; 37,5 i elektrofagene), overtid uten tillegg (§ 10-6; 50 % etter allmenngjøringen), endringer innen én måned (§ 14-8), lønn uten beløp (§ 14-6). Lovlig: prøvetid seks måneder (§ 15-6), gjensidig frist én måned (§ 15-3)</t>
   </si>
   <si>
     <t xml:space="preserve">1A e) 300 overtidstimer</t>
@@ -667,13 +671,19 @@
     <t xml:space="preserve">212 − 200 = 12 timer (§ 10-6 fjerde ledd). 300 timer krever skriftlig avtale med tillitsvalgte i tariffbundet virksomhet (femte ledd)</t>
   </si>
   <si>
-    <t xml:space="preserve">1B e) Ronny</t>
+    <t xml:space="preserve">1B e) Betalt overtid etter tariffavtalen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 − 37,5 = 14,5 timer med overtidstillegg: 8,5 timer mandag til fredag med 50 % og lørdagens 6 timer med 100 %, fordi Nordlys har fri hver lørdag (Landsoverenskomsten for elektrofagene: for fagarbeider faste tillegg på 189,17 kr og 378,33 kr per time fra 1. mai 2026). Lovens 12 timer brukes bare for grensene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1B f) Ronny</t>
   </si>
   <si>
     <t xml:space="preserve">Drøfte behovet med de tillitsvalgte før overtiden settes i gang (§ 10-6 tredje ledd)</t>
   </si>
   <si>
-    <t xml:space="preserve">1B f) Til Kari</t>
+    <t xml:space="preserve">1B g) Til Kari</t>
   </si>
   <si>
     <t xml:space="preserve">Overtid krever et særlig og tidsavgrenset behov (§ 10-6 første ledd). Grensene 10 timer per sju dager og 200 timer per 52 uker gjelder uansett betaling (fjerde ledd). Fullt forsvarlig arbeidsmiljø (§ 4-1); arbeidsmengde og tidspress er psykososialt arbeidsmiljø (§ 4-3 andre ledd)</t>
@@ -748,7 +758,7 @@
     <t xml:space="preserve">15 300 × 1,15 = 17 595 kr (§ 32 andre ledd)</t>
   </si>
   <si>
-    <t xml:space="preserve">2B b) Vernet hos kunde 1</t>
+    <t xml:space="preserve">2B b) Underfordelingen hos kunde 1</t>
   </si>
   <si>
     <t xml:space="preserve">Kontakte kunden først (§ 9 første ledd). Bare fare for vesentlig skade gir rett til å gjøre det uten videre (tredje ledd)</t>
@@ -757,7 +767,7 @@
     <t xml:space="preserve">2B c) Kunde 1 i alt</t>
   </si>
   <si>
-    <t xml:space="preserve">15 300 + 2 500 = 17 800 kr. Fast pris for oppdraget pluss tilleggsarbeid etter §§ 9 og 33</t>
+    <t xml:space="preserve">15 300 + 5 000 = 20 300 kr. Fast pris for oppdraget pluss tilleggsarbeid etter §§ 9 og 33</t>
   </si>
   <si>
     <t xml:space="preserve">2B d) 15 % som fribeløp</t>
@@ -1531,7 +1541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
@@ -1557,7 +1567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
@@ -1588,7 +1598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>25</v>
       </c>
@@ -1660,7 +1670,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1718,7 +1728,7 @@
         <v>39</v>
       </c>
       <c r="G24" s="17" t="str">
-        <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(560000/1800*1.4,0)))&lt;=1,"Riktig.",IF(ABS(C24-(ROUND(560000/1800*0.4,0)))&lt;=1,"Du har regnet bare tillegget. Overtidslønna er timelønna pluss tillegget: timelønn × 1,40.",IF(ABS(C24-(ROUND(560000/1800,0)))&lt;=1,"Det er vanlig timelønn. Overtid skal ha et tillegg på minst 40 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(560000/1800*1.5,0)))&lt;=1,"Riktig.",IF(ABS(C24-(ROUND(560000/1800*0.5,0)))&lt;=1,"Du har regnet bare tillegget. Overtidslønna er timelønna pluss tillegget: timelønn × 1,50.",IF(ABS(C24-(ROUND(560000/1800*1.4,0)))&lt;=1,"Du har brukt lovens minste tillegg på 40 prosent. Fjell er elektrobedrift, og allmenngjøringen av Landsoverenskomsten for elektrofagene gir 50 prosent også for bedrifter uten tariffavtale.",IF(ABS(C24-(ROUND(560000/1800,0)))&lt;=1,"Det er vanlig timelønn. Overtid skal ha et tillegg, i elektrofagene 50 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1738,7 +1748,7 @@
       </c>
       <c r="C27" s="19"/>
       <c r="G27" s="17" t="str">
-        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ikke lovlig","Riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den.","Ikke riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den."))</f>
+        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ikke lovlig","Riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd), og i elektrofagene er ordinær arbeidstid 37,5 timer (allmenngjøringen for elektrofagene). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den.","Ikke riktig. Alminnelig arbeidstid er høyst 9 timer i døgnet og 40 timer i uka (§ 10-4 første ledd), og i elektrofagene er ordinær arbeidstid 37,5 timer (allmenngjøringen for elektrofagene). Loven er et minstekrav; montøren kan ikke avtale seg bort fra den."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -1748,7 +1758,7 @@
       </c>
       <c r="C28" s="19"/>
       <c r="G28" s="17" t="str">
-        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Ikke lovlig","Riktig. Overtid skal betales med et tillegg på minst 40 prosent (§ 10-6 ellevte ledd), og avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m).","Ikke riktig. Overtid skal betales med et tillegg på minst 40 prosent (§ 10-6 ellevte ledd), og avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m)."))</f>
+        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Ikke lovlig","Riktig. Overtid skal betales med tillegg: loven krever minst 40 prosent (§ 10-6 ellevte ledd), og allmenngjøringen for elektrofagene gir 50 prosent. Avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m).","Ikke riktig. Overtid skal betales med tillegg: loven krever minst 40 prosent (§ 10-6 ellevte ledd), og allmenngjøringen for elektrofagene gir 50 prosent. Avtalen skal si hvordan arbeid utover avtalt tid betales (§ 14-6 første ledd bokstav m)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -1845,7 +1855,7 @@
     </row>
     <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="str">
-        <f aca="false">IF(C39="JA","Hint: a: fristen gikk ut 1 + 7 = 8. august; 20 − 8 = 12 dager. b: 560 000 / 1 800 = 311 kr. c: 311,11 × 1,40 = 436 kr. d: 42 timer, overtid uten tillegg, «innen én måned» og «lønn etter avtale» er ikke lovlige; prøvetid seks måneder og én måneds frist er lovlige.","")</f>
+        <f aca="false">IF(C39="JA","Hint: a: fristen gikk ut 1 + 7 = 8. august; 20 − 8 = 12 dager. b: 560 000 / 1 800 = 311 kr. c: 311,11 × 1,50 = 467 kr. d: 42 timer, overtid uten tillegg, «innen én måned» og «lønn etter avtale» er ikke lovlige; prøvetid seks måneder og én måneds frist er lovlige.","")</f>
         <v/>
       </c>
       <c r="C40" s="23"/>
@@ -2000,7 +2010,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:Z39"/>
+  <dimension ref="B1:Z40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2052,7 +2062,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>55</v>
       </c>
@@ -2072,7 +2082,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
         <v>56</v>
       </c>
@@ -2092,7 +2102,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>57</v>
       </c>
@@ -2185,7 +2195,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
         <v>68</v>
       </c>
@@ -2217,7 +2227,7 @@
         <v>70</v>
       </c>
       <c r="G25" s="17" t="str">
-        <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(52-40),"Riktig.",IF(ABS(C25-(52-40+3.5))&lt;=0,"Du har telt timene over 9 per dag én gang til. De ligger allerede inni de 52 timene. Overtiden er 52 − 40 = 12.",IF(ABS(C25-(52-37.5))&lt;=0,"Du har regnet fra avtalt arbeidstid, 37,5. Lovens overtid regnes fra lovens grense, 40 timer (§ 10-6 andre ledd). Timene mellom 37,5 og 40 er arbeid utover avtalt tid, men ikke overtid etter loven.",IF(ABS(C25-(3.5))&lt;=0,"Det er bare timene over 9 per dag. Uka er på 52 timer, og alt over 40 er overtid.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(52-40),"Riktig.",IF(ABS(C25-(52-40+3.5))&lt;=0,"Du har telt timene over 9 per dag én gang til. De ligger allerede inni de 52 timene. Overtiden er 52 − 40 = 12.",IF(ABS(C25-(52-37.5))&lt;=0,"14,5 er timene Nordlys skal betale overtidstillegg for etter tariffavtalen (alt over 37,5), og det regner du i e. Her spør vi om lovens grenser for hvor mye overtid som er lov, og de telles fra lovens 40 timer (§ 10-6 andre ledd).",IF(ABS(C25-(3.5))&lt;=0,"Det er bare timene over 9 per dag. Uka er på 52 timer, og alt over 40 er overtid.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2247,33 +2257,38 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
+    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="G29" s="17" t="str">
-        <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Drøfte behovet for overtid med de tillitsvalgte før den settes i gang (§ 10-6 tredje ledd)","Riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtid gir dessuten minst 40 % tillegg (ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd).","Ikke riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtid gir dessuten minst 40 % tillegg (ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd)."))</f>
+      <c r="C28" s="26"/>
+      <c r="D28" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(C28=(52-37.5),"Riktig.",IF(ABS(C28-(52-40))&lt;=0,"12 er lovens overtid, som brukes for grensene. Tariffavtalen betaler overtidstillegg for alt over ordinær arbeidstid, 37,5 timer.",IF(ABS(C28-(6))&lt;=0,"Det er bare lørdagen. Også timene over 7,5 per dag mandag til fredag er overtid etter tariffavtalen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <v>Skriv svaret i den gule cellen.</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="17" t="str">
+        <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Drøfte behovet for overtid med de tillitsvalgte før den settes i gang (§ 10-6 tredje ledd)","Riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtiden betales med 50 % tillegg etter tariffavtalen (loven krever minst 40 %, ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd).","Ikke riktig. Før overtid settes i gang, skal arbeidsgiver drøfte nødvendigheten med de tillitsvalgte når det er mulig (§ 10-6 tredje ledd). Overtiden betales med 50 % tillegg etter tariffavtalen (loven krever minst 40 %, ellevte ledd), og den som ber om det av helsemessige eller vektige sosiale grunner, skal fritas (tiende ledd)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="20"/>
@@ -2291,43 +2306,51 @@
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="21" t="str">
-        <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("200",B32)),ISNUMBER(SEARCH("behov",B32))),"Bra: du har med både at overtid krever et særlig og tidsavgrenset behov, og grensen på 200 timer i 52 uker. Betaling gjør ikke ulovlig overtid lovlig.",IF(OR(ISNUMBER(SEARCH("200",B32)),ISNUMBER(SEARCH("behov",B32))),"Du er på sporet. Ta med både vilkåret (særlig og tidsavgrenset behov, § 10-6 første ledd) og grensen (200 timer i 52 uker uten avtale, fjerde ledd).","Tips: overtid er lov bare når det er et særlig og tidsavgrenset behov (§ 10-6 første ledd). Fast overtid hver uke er underbemanning. Og grensene gjelder uansett lønn: 10 timer per sju dager og 200 timer per 52 uker (fjerde ledd). Arbeidsmiljøet skal være fullt forsvarlig, og arbeidsmengde og tidspress er en del av det psykososiale arbeidsmiljøet (§§ 4-1 og 4-3).")))</f>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="21" t="str">
+        <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("200",B33)),ISNUMBER(SEARCH("behov",B33))),"Bra: du har med både at overtid krever et særlig og tidsavgrenset behov, og grensen på 200 timer i 52 uker. Betaling gjør ikke ulovlig overtid lovlig.",IF(OR(ISNUMBER(SEARCH("200",B33)),ISNUMBER(SEARCH("behov",B33))),"Du er på sporet. Ta med både vilkåret (særlig og tidsavgrenset behov, § 10-6 første ledd) og grensen (200 timer i 52 uker uten avtale, fjerde ledd).","Tips: overtid er lov bare når det er et særlig og tidsavgrenset behov (§ 10-6 første ledd). Fast overtid hver uke er underbemanning. Og grensene gjelder uansett lønn: 10 timer per sju dager og 200 timer per 52 uker (fjerde ledd). Arbeidsmiljøet skal være fullt forsvarlig, og arbeidsmengde og tidspress er en del av det psykososiale arbeidsmiljøet (§§ 4-1 og 4-3).")))</f>
         <v/>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="s">
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="19"/>
-    </row>
-    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23" t="str">
-        <f aca="false">IF(C36="JA","Hint: a: onsdag 11,5 − 9 = 2,5 og fredag 10 − 9 = 1, til sammen 3,5. b: 52 − 40 = 12 (ikke 12 + 3,5 = 15,5). c: 12 − 10 = 2. d: 212 − 200 = 12.","")</f>
+      <c r="C37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="23" t="str">
+        <f aca="false">IF(C37="JA","Hint: a: onsdag 11,5 − 9 = 2,5 og fredag 10 − 9 = 1, til sammen 3,5. b: 52 − 40 = 12 (ikke 12 + 3,5 = 15,5). c: 12 − 10 = 2. d: 212 − 200 = 12. e: 52 − 37,5 = 14,5.","")</f>
         <v/>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-    </row>
-    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="7" t="s">
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2341,11 +2364,11 @@
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B40:G40"/>
   </mergeCells>
   <conditionalFormatting sqref="G24">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -2379,20 +2402,28 @@
       <formula>AND(G27&lt;&gt;"",LEFT(G27,6)&lt;&gt;"Riktig",LEFT(G27,5)&lt;&gt;"Skriv")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
+  <conditionalFormatting sqref="G28">
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G29,6)="Riktig"</formula>
+      <formula>LEFT(G28,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT(G29,4)="Ikke"</formula>
+      <formula>AND(G28&lt;&gt;"",LEFT(G28,6)&lt;&gt;"Riktig",LEFT(G28,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>LEFT(G30,6)="Riktig"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>LEFT(G30,4)="Ikke"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
       <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
       <formula1>"JA,NEI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2425,12 +2456,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z1" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2438,7 +2469,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="Z2" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2451,7 +2482,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="Z3" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,12 +2495,12 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="Z4" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -2477,7 +2508,7 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="Z5" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2490,12 +2521,12 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="Z6" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -2503,12 +2534,12 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="Z7" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z8" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2521,12 +2552,12 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="Z9" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -2534,78 +2565,78 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="Z10" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>27</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>2020</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>2027</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>41</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>3</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z17" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2618,12 +2649,12 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="Z18" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -2633,11 +2664,11 @@
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(6),"Riktig.",IF(ABS(C21-(7))&lt;=0,"Fra august 2020 til mars 2027 er det 6 år og 7 måneder. Det sjuende året er ikke fullt før august 2027.",IF(ABS(C21-(5))&lt;=0,"Tell en gang til: august 2020 til august 2026 er seks år, og mars 2027 er etter det.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -2646,11 +2677,11 @@
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(C22=(2),"Riktig.",IF(ABS(C22-(1))&lt;=0,"Én måned er hovedregelen under fem års ansettelse. Jonas har over fem år: minst to måneder (andre ledd).",IF(ABS(C22-(3))&lt;=0,"Tre måneder gjelder fra ti års sammenhengende ansettelse. Nordlys startet i 2019, så ingen har ti år ennå.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -2659,7 +2690,7 @@
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" s="19"/>
       <c r="G24" s="17" t="str">
@@ -2669,7 +2700,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -2679,7 +2710,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" s="19"/>
       <c r="G27" s="17" t="str">
@@ -2689,7 +2720,7 @@
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="19"/>
       <c r="G28" s="17" t="str">
@@ -2699,7 +2730,7 @@
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="19"/>
       <c r="G29" s="17" t="str">
@@ -2709,7 +2740,7 @@
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" s="19"/>
       <c r="G30" s="17" t="str">
@@ -2719,7 +2750,7 @@
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="19"/>
       <c r="G31" s="17" t="str">
@@ -2729,7 +2760,7 @@
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="19"/>
       <c r="G32" s="17" t="str">
@@ -2739,7 +2770,7 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="19"/>
       <c r="G34" s="17" t="str">
@@ -2749,7 +2780,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -2984,12 +3015,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z1" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2997,7 +3028,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="Z2" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3010,7 +3041,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="Z3" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3025,7 +3056,7 @@
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3045,7 +3076,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3065,7 +3096,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -3078,12 +3109,12 @@
         <v>26</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>36000</v>
@@ -3091,7 +3122,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>42300</v>
@@ -3099,7 +3130,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>15</v>
@@ -3117,7 +3148,7 @@
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3127,11 +3158,11 @@
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(C19=(36000*1.15),"Riktig.",IF(ABS(C19-(42300*1.15))&lt;=0,"Du har lagt 15 prosent på fakturaen. Prosenten regnes av prisoverslaget.",IF(ABS(C19-(36000*0.15))&lt;=0,"Du har regnet bare tillegget. Taket er overslaget pluss 15 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -3140,11 +3171,11 @@
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Skriv svaret i den gule cellen.",IF(ABS(C20-(ROUND((42300-36000)/36000*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C20-(ROUND((42300-36000)/42300*100,1)))&lt;=0.1,"Du har delt på fakturaen. Overskridelsen skal måles mot prisoverslaget, 36 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
@@ -3153,11 +3184,11 @@
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(C21=(42300-36000*1.15),"Riktig.",IF(ABS(C21-(42300-36000))&lt;=0,"Det er hele overskridelsen. Hvor mye av den kunden slipper, avhenger av om overskridelsen var vesentlig og av bruddet på § 7. Det hun i alle fall slipper, er det som ligger over taket.",IF(ABS(C21-(36000*0.15))&lt;=0,"Det er 15 prosent av overslaget, altså rommet opp til taket, ikke det som ligger over.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -3166,7 +3197,7 @@
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" s="19"/>
       <c r="G23" s="17" t="str">
@@ -3176,7 +3207,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -3334,12 +3365,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z1" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -3347,7 +3378,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="Z2" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3360,7 +3391,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="Z3" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3373,12 +3404,12 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="Z4" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3386,7 +3417,7 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="Z5" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3399,12 +3430,12 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="Z6" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3412,12 +3443,12 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="Z7" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z8" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3430,12 +3461,12 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="Z9" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -3443,7 +3474,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="Z10" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3451,48 +3482,48 @@
         <v>26</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>15300</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>15</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z15" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3505,12 +3536,12 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="Z16" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3518,38 +3549,38 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="Z17" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z18" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(C19=(15300*1.15),"Riktig.",IF(ABS(C19-(15300))&lt;=0,"Det er overslaget. Et prisoverslag kan overskrides noe, men ikke vesentlig, og i alle fall ikke med mer enn 15 prosent.",IF(ABS(C19-(15300*0.15))&lt;=0,"Du har regnet bare tillegget. Taket er overslaget pluss 15 prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z20" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="19"/>
       <c r="G21" s="17" t="str">
@@ -3557,38 +3588,38 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z22" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" s="17" t="str">
-        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(15300+2500),"Riktig.",IF(ABS(C23-(15300*1.15+2500))&lt;=0,"Du har lagt 15 prosent på en fast pris. Fast pris er fast; 15 prosent gjelder bare prisoverslag.",IF(ABS(C23-(15300))&lt;=0,"Du har glemt tilleggsarbeidet. Tilleggsarbeid som er avtalt etter § 9, kan kreves betalt (§ 33).","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(15300+5000),"Riktig.",IF(ABS(C23-(15300*1.15+5000))&lt;=0,"Du har lagt 15 prosent på en fast pris. Fast pris er fast; 15 prosent gjelder bare prisoverslag.",IF(ABS(C23-(15300))&lt;=0,"Du har glemt tilleggsarbeidet. Tilleggsarbeid som er avtalt etter § 9, kan kreves betalt (§ 33).","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z24" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C25" s="19"/>
       <c r="G25" s="17" t="str">
@@ -3596,17 +3627,17 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z26" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -3614,12 +3645,12 @@
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="Z27" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" s="19"/>
       <c r="G28" s="17" t="str">
@@ -3627,12 +3658,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z28" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C29" s="19"/>
       <c r="G29" s="17" t="str">
@@ -3640,12 +3671,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="19"/>
       <c r="G30" s="17" t="str">
@@ -3653,12 +3684,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z30" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C31" s="19"/>
       <c r="G31" s="17" t="str">
@@ -3666,12 +3697,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C32" s="19"/>
       <c r="G32" s="17" t="str">
@@ -3681,7 +3712,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -3715,7 +3746,7 @@
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="21" t="str">
-        <f aca="false">IF(LEN(B35)&lt;40,"",IF(AND(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Bra: du velger fast pris og sier at den skal stå skriftlig. Si også hva som ikke er med i prisen, og at slikt avtales med kunden før det gjøres (§ 9).",IF(OR(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Du er på sporet. En standardpakke med kjent tidsbruk passer for fast pris, og prisformen må stå skriftlig med ord, fordi det er håndverkeren som må godtgjøre hva som ble lovet.","Tips: en standardpakke med kjent tidsbruk passer for fast pris: kunden vet hva hun får, og Fjell bærer risikoen for tiden. Skriv «fast pris, inkludert merverdiavgift» med ord, og si hva som ikke er med (nytt vern, ny kurs) og at det avtales med kunden før det gjøres (§ 9). «Ca. 15 000» bør ut av malen.")))</f>
+        <f aca="false">IF(LEN(B35)&lt;40,"",IF(AND(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Bra: du velger fast pris og sier at den skal stå skriftlig. Si også hva som ikke er med i prisen, og at slikt avtales med kunden før det gjøres (§ 9).",IF(OR(ISNUMBER(SEARCH("fast",B35)),ISNUMBER(SEARCH("skriftlig",B35))),"Du er på sporet. En standardpakke med kjent tidsbruk passer for fast pris, og prisformen må stå skriftlig med ord, fordi det er håndverkeren som må godtgjøre hva som ble lovet.","Tips: en standardpakke med kjent tidsbruk passer for fast pris: kunden vet hva hun får, og Fjell bærer risikoen for tiden. Skriv «fast pris, inkludert merverdiavgift» med ord, og si hva som ikke er med (for eksempel ny underfordeling når skapet er fullt; egen kurs og jordfeilvern er påbudt og ligger i prisen) og at det avtales med kunden før det gjøres (§ 9). «Ca. 15 000» bør ut av malen.")))</f>
         <v/>
       </c>
       <c r="C38" s="21"/>
@@ -3732,7 +3763,7 @@
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="str">
-        <f aca="false">IF(C39="JA","Hint: a: 15 300 × 1,15 = 17 595. b: kontakt kunden først (§ 9 første ledd). c: 15 300 + 2 500 = 17 800. d: nei, 15 % er et tak. e: fast pris, prisoverslag, uforpliktende prisantydning, høyeste pris, gjengs pris.","")</f>
+        <f aca="false">IF(C39="JA","Hint: a: 15 300 × 1,15 = 17 595. b: kontakt kunden først (§ 9 første ledd). c: 15 300 + 5 000 = 20 300. d: nei, 15 % er et tak. e: fast pris, prisoverslag, uforpliktende prisantydning, høyeste pris, gjengs pris.","")</f>
         <v/>
       </c>
       <c r="C40" s="23"/>
@@ -3909,7 +3940,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -3930,7 +3961,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="Z3" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3948,7 +3979,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3969,12 +4000,12 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="Z6" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3992,7 +4023,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -4000,12 +4031,12 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="Z9" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -4023,7 +4054,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -4031,12 +4062,12 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="Z12" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="19"/>
       <c r="G13" s="17" t="str">
@@ -4049,7 +4080,7 @@
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="19"/>
       <c r="G14" s="17" t="str">
@@ -4062,7 +4093,7 @@
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="19"/>
       <c r="G15" s="17" t="str">
@@ -4070,12 +4101,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="19"/>
       <c r="G16" s="17" t="str">
@@ -4088,7 +4119,7 @@
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C17" s="19"/>
       <c r="G17" s="17" t="str">
@@ -4101,7 +4132,7 @@
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="19"/>
       <c r="G18" s="17" t="str">
@@ -4109,12 +4140,12 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="19"/>
       <c r="G19" s="17" t="str">
@@ -4127,7 +4158,7 @@
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C20" s="19"/>
       <c r="G20" s="17" t="str">
@@ -4140,7 +4171,7 @@
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="19"/>
       <c r="G21" s="17" t="str">
@@ -4148,7 +4179,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4158,7 +4189,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -4171,7 +4202,7 @@
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -4179,12 +4210,12 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="Z24" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="19"/>
       <c r="G25" s="17" t="str">
@@ -4197,7 +4228,7 @@
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="19"/>
       <c r="G26" s="17" t="str">
@@ -4210,7 +4241,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="19"/>
       <c r="G27" s="17" t="str">
@@ -4218,17 +4249,17 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z28" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -4236,7 +4267,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="Z29" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4247,7 +4278,7 @@
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="Z30" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4258,7 +4289,7 @@
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
       <c r="Z31" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4269,7 +4300,7 @@
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
       <c r="Z32" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4283,7 +4314,7 @@
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="Z33" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4292,7 +4323,7 @@
       </c>
       <c r="C34" s="19"/>
       <c r="Z34" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4306,12 +4337,12 @@
       <c r="F35" s="23"/>
       <c r="G35" s="23"/>
       <c r="Z35" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z36" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4508,7 +4539,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:D36"/>
+  <dimension ref="B2:D37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4519,332 +4550,343 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>12</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C7" s="30" t="n">
         <v>311</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C11" s="30" t="n">
         <v>3.5</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>12</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C13" s="30" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C14" s="30" t="n">
         <v>12</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="30"/>
+        <v>207</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>14.5</v>
+      </c>
       <c r="D15" s="29" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="29" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="30" t="n">
-        <v>6</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C17" s="30"/>
       <c r="D17" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C19" s="30"/>
+        <v>215</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>2</v>
+      </c>
       <c r="D19" s="29" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>41400</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C23" s="30"/>
       <c r="D23" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="30" t="n">
-        <v>17.5</v>
+        <v>41400</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C25" s="30" t="n">
-        <v>900</v>
+        <v>17.5</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="C26" s="30"/>
+        <v>229</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>900</v>
+      </c>
       <c r="D26" s="29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>17595</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C28" s="30"/>
       <c r="D28" s="29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="C29" s="30"/>
+        <v>234</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>17595</v>
+      </c>
       <c r="D29" s="29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="C30" s="30" t="n">
-        <v>17800</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C30" s="30"/>
       <c r="D30" s="29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31" s="30"/>
+        <v>238</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>20300</v>
+      </c>
       <c r="D31" s="29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C32" s="30"/>
       <c r="D32" s="29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="29" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="29" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="29" t="s">
-        <v>248</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="29" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
+++ b/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
@@ -990,7 +990,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1113,6 +1113,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1400,7 +1404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1425,42 +1429,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1633,8 +1637,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="13" t="n">
@@ -1665,8 +1669,8 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="13" t="n">
@@ -1683,7 +1687,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
         <v>35</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
         <v>40</v>
       </c>
@@ -1732,7 +1736,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
         <v>41</v>
       </c>
@@ -2195,7 +2199,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
         <v>68</v>
       </c>
@@ -2257,7 +2261,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
         <v>74</v>
       </c>
@@ -2652,7 +2656,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>95</v>
       </c>
@@ -2698,7 +2702,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
         <v>101</v>
       </c>
@@ -2718,7 +2722,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
         <v>103</v>
       </c>
@@ -2748,7 +2752,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="14" t="s">
         <v>106</v>
       </c>
@@ -2768,7 +2772,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="14" t="s">
         <v>108</v>
       </c>
@@ -2778,7 +2782,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="s">
         <v>109</v>
       </c>
@@ -3146,7 +3150,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>121</v>
       </c>
@@ -3169,7 +3173,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
         <v>124</v>
       </c>
@@ -3195,7 +3199,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
         <v>127</v>
       </c>
@@ -3499,8 +3503,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B13" t="s">
         <v>145</v>
       </c>
       <c r="C13" s="13" t="n">
@@ -3510,8 +3514,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B14" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="13" t="n">
@@ -3539,7 +3543,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>147</v>
       </c>
@@ -3578,7 +3582,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
         <v>149</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
         <v>150</v>
       </c>
@@ -3617,7 +3621,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
         <v>151</v>
       </c>
@@ -3635,7 +3639,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
         <v>152</v>
       </c>
@@ -4052,7 +4056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
         <v>165</v>
       </c>
@@ -4130,7 +4134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="14" t="s">
         <v>171</v>
       </c>

--- a/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
+++ b/pensum/ol20/OL20_Noen_viktige_lover_Oppgaver_v6.xlsx
@@ -990,7 +990,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1113,10 +1113,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1404,7 +1400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1429,42 +1425,42 @@
         <v>6</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1637,8 +1633,8 @@
         <v>18</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="31" r="B13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="13" t="n">
@@ -1669,8 +1665,8 @@
         <v>1800</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="31" r="B17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="13" t="n">
@@ -1687,7 +1683,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row ht="75.75" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
         <v>35</v>
       </c>
@@ -1723,7 +1719,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
         <v>40</v>
       </c>
@@ -1736,7 +1732,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
         <v>41</v>
       </c>
@@ -2199,7 +2195,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row ht="90" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
         <v>68</v>
       </c>
@@ -2261,7 +2257,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
         <v>74</v>
       </c>
@@ -2656,7 +2652,7 @@
         <v>94</v>
       </c>
     </row>
-    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>95</v>
       </c>
@@ -2702,7 +2698,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
         <v>101</v>
       </c>
@@ -2722,7 +2718,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
         <v>103</v>
       </c>
@@ -2752,7 +2748,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="14" t="s">
         <v>106</v>
       </c>
@@ -2772,7 +2768,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="14" t="s">
         <v>108</v>
       </c>
@@ -2782,7 +2778,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="36" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="s">
         <v>109</v>
       </c>
@@ -3150,7 +3146,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
     </row>
-    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>121</v>
       </c>
@@ -3173,7 +3169,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
         <v>124</v>
       </c>
@@ -3199,7 +3195,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
         <v>127</v>
       </c>
@@ -3503,8 +3499,8 @@
         <v>138</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="31" r="B13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C13" s="13" t="n">
@@ -3514,8 +3510,8 @@
         <v>139</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="31" r="B14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="13" t="n">
@@ -3543,7 +3539,7 @@
         <v>143</v>
       </c>
     </row>
-    <row ht="75.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>147</v>
       </c>
@@ -3582,7 +3578,7 @@
         <v>142</v>
       </c>
     </row>
-    <row ht="60.75" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
         <v>149</v>
       </c>
@@ -3600,7 +3596,7 @@
         <v>138</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
         <v>150</v>
       </c>
@@ -3621,7 +3617,7 @@
         <v>140</v>
       </c>
     </row>
-    <row ht="60.75" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
         <v>151</v>
       </c>
@@ -3639,7 +3635,7 @@
         <v>143</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
         <v>152</v>
       </c>
@@ -4056,7 +4052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
         <v>165</v>
       </c>
@@ -4134,7 +4130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="14" t="s">
         <v>171</v>
       </c>
